--- a/artfynd/A 45735-2025 artfynd.xlsx
+++ b/artfynd/A 45735-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>129120200</v>
       </c>
       <c r="B3" t="n">
-        <v>85195</v>
+        <v>85198</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129120162</v>
       </c>
       <c r="B4" t="n">
-        <v>92321</v>
+        <v>92326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>129120179</v>
       </c>
       <c r="B5" t="n">
-        <v>91508</v>
+        <v>91511</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>129120312</v>
       </c>
       <c r="B6" t="n">
-        <v>92083</v>
+        <v>92088</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45735-2025 artfynd.xlsx
+++ b/artfynd/A 45735-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>129120200</v>
       </c>
       <c r="B3" t="n">
-        <v>85198</v>
+        <v>85201</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129120162</v>
       </c>
       <c r="B4" t="n">
-        <v>92326</v>
+        <v>92329</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>129120179</v>
       </c>
       <c r="B5" t="n">
-        <v>91511</v>
+        <v>91514</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>129120312</v>
       </c>
       <c r="B6" t="n">
-        <v>92088</v>
+        <v>92091</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45735-2025 artfynd.xlsx
+++ b/artfynd/A 45735-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>129120200</v>
       </c>
       <c r="B3" t="n">
-        <v>85201</v>
+        <v>85205</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129120162</v>
       </c>
       <c r="B4" t="n">
-        <v>92329</v>
+        <v>92336</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>129120179</v>
       </c>
       <c r="B5" t="n">
-        <v>91514</v>
+        <v>91521</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>129120312</v>
       </c>
       <c r="B6" t="n">
-        <v>92091</v>
+        <v>92098</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45735-2025 artfynd.xlsx
+++ b/artfynd/A 45735-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>129120200</v>
       </c>
       <c r="B3" t="n">
-        <v>85205</v>
+        <v>85210</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129120162</v>
       </c>
       <c r="B4" t="n">
-        <v>92336</v>
+        <v>92343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>129120179</v>
       </c>
       <c r="B5" t="n">
-        <v>91521</v>
+        <v>91528</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>129120312</v>
       </c>
       <c r="B6" t="n">
-        <v>92098</v>
+        <v>92105</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45735-2025 artfynd.xlsx
+++ b/artfynd/A 45735-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>129120200</v>
       </c>
       <c r="B3" t="n">
-        <v>85210</v>
+        <v>85212</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129120162</v>
       </c>
       <c r="B4" t="n">
-        <v>92343</v>
+        <v>92345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>129120179</v>
       </c>
       <c r="B5" t="n">
-        <v>91528</v>
+        <v>91530</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>129120312</v>
       </c>
       <c r="B6" t="n">
-        <v>92105</v>
+        <v>92107</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45735-2025 artfynd.xlsx
+++ b/artfynd/A 45735-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>129120200</v>
       </c>
       <c r="B3" t="n">
-        <v>85212</v>
+        <v>85213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129120162</v>
       </c>
       <c r="B4" t="n">
-        <v>92345</v>
+        <v>92359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>129120179</v>
       </c>
       <c r="B5" t="n">
-        <v>91530</v>
+        <v>91528</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>129120312</v>
       </c>
       <c r="B6" t="n">
-        <v>92107</v>
+        <v>92122</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45735-2025 artfynd.xlsx
+++ b/artfynd/A 45735-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>129120162</v>
       </c>
       <c r="B4" t="n">
-        <v>92359</v>
+        <v>92360</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>129120312</v>
       </c>
       <c r="B6" t="n">
-        <v>92122</v>
+        <v>92123</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45735-2025 artfynd.xlsx
+++ b/artfynd/A 45735-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>129120200</v>
       </c>
       <c r="B3" t="n">
-        <v>85213</v>
+        <v>85220</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129120162</v>
       </c>
       <c r="B4" t="n">
-        <v>92360</v>
+        <v>92363</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>129120179</v>
       </c>
       <c r="B5" t="n">
-        <v>91528</v>
+        <v>91531</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>129120312</v>
       </c>
       <c r="B6" t="n">
-        <v>92123</v>
+        <v>92126</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45735-2025 artfynd.xlsx
+++ b/artfynd/A 45735-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>129120200</v>
       </c>
       <c r="B3" t="n">
-        <v>85220</v>
+        <v>85222</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129120162</v>
       </c>
       <c r="B4" t="n">
-        <v>92363</v>
+        <v>92365</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>129120179</v>
       </c>
       <c r="B5" t="n">
-        <v>91531</v>
+        <v>91533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>129120312</v>
       </c>
       <c r="B6" t="n">
-        <v>92126</v>
+        <v>92128</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45735-2025 artfynd.xlsx
+++ b/artfynd/A 45735-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>129120162</v>
       </c>
       <c r="B4" t="n">
-        <v>92365</v>
+        <v>92369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>129120179</v>
       </c>
       <c r="B5" t="n">
-        <v>91533</v>
+        <v>91537</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>129120312</v>
       </c>
       <c r="B6" t="n">
-        <v>92128</v>
+        <v>92132</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45735-2025 artfynd.xlsx
+++ b/artfynd/A 45735-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>129120200</v>
       </c>
       <c r="B3" t="n">
-        <v>85222</v>
+        <v>85223</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129120162</v>
       </c>
       <c r="B4" t="n">
-        <v>92369</v>
+        <v>92370</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>129120179</v>
       </c>
       <c r="B5" t="n">
-        <v>91537</v>
+        <v>91538</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>129120312</v>
       </c>
       <c r="B6" t="n">
-        <v>92132</v>
+        <v>92133</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45735-2025 artfynd.xlsx
+++ b/artfynd/A 45735-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>129120162</v>
       </c>
       <c r="B4" t="n">
-        <v>92370</v>
+        <v>92373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>129120179</v>
       </c>
       <c r="B5" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>129120312</v>
       </c>
       <c r="B6" t="n">
-        <v>92133</v>
+        <v>92136</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45735-2025 artfynd.xlsx
+++ b/artfynd/A 45735-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1213,6 +1213,685 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129909309</v>
+      </c>
+      <c r="B7" t="n">
+        <v>110705</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219677</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Murgröna</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hedera helix</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Knösö, Bl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>541705</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6225086</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Karlskrona</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lösen</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129909315</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91558</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Knösö, Bl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>541449</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6225090</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Karlskrona</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lösen</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129909308</v>
+      </c>
+      <c r="B9" t="n">
+        <v>110705</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219677</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Murgröna</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hedera helix</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Knösö, Bl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>541609</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6225184</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Karlskrona</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lösen</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129909319</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91558</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Knösö, Bl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>541676</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6225123</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Karlskrona</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lösen</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129909310</v>
+      </c>
+      <c r="B11" t="n">
+        <v>110705</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219677</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Murgröna</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hedera helix</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Knösö, Bl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>541322</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6225055</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Karlskrona</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lösen</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129909317</v>
+      </c>
+      <c r="B12" t="n">
+        <v>96381</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Knösö, Bl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>541548</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6225086</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Karlskrona</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lösen</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129909316</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91558</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Knösö, Bl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>541530</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6225095</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Karlskrona</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lösen</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45735-2025 artfynd.xlsx
+++ b/artfynd/A 45735-2025 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>129909309</v>
       </c>
       <c r="B7" t="n">
-        <v>110705</v>
+        <v>110735</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>129909308</v>
       </c>
       <c r="B9" t="n">
-        <v>110705</v>
+        <v>110735</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>129909310</v>
       </c>
       <c r="B11" t="n">
-        <v>110705</v>
+        <v>110735</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>129909317</v>
       </c>
       <c r="B12" t="n">
-        <v>96381</v>
+        <v>96386</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 45735-2025 artfynd.xlsx
+++ b/artfynd/A 45735-2025 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>129909309</v>
       </c>
       <c r="B7" t="n">
-        <v>110735</v>
+        <v>110739</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>129909315</v>
       </c>
       <c r="B8" t="n">
-        <v>91558</v>
+        <v>91561</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>129909308</v>
       </c>
       <c r="B9" t="n">
-        <v>110735</v>
+        <v>110739</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>129909319</v>
       </c>
       <c r="B10" t="n">
-        <v>91558</v>
+        <v>91561</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>129909310</v>
       </c>
       <c r="B11" t="n">
-        <v>110735</v>
+        <v>110739</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>129909317</v>
       </c>
       <c r="B12" t="n">
-        <v>96386</v>
+        <v>96390</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>129909316</v>
       </c>
       <c r="B13" t="n">
-        <v>91558</v>
+        <v>91561</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 45735-2025 artfynd.xlsx
+++ b/artfynd/A 45735-2025 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>129909309</v>
       </c>
       <c r="B7" t="n">
-        <v>110739</v>
+        <v>110742</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>129909315</v>
       </c>
       <c r="B8" t="n">
-        <v>91561</v>
+        <v>91564</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>129909308</v>
       </c>
       <c r="B9" t="n">
-        <v>110739</v>
+        <v>110742</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>129909319</v>
       </c>
       <c r="B10" t="n">
-        <v>91561</v>
+        <v>91564</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>129909310</v>
       </c>
       <c r="B11" t="n">
-        <v>110739</v>
+        <v>110742</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>129909317</v>
       </c>
       <c r="B12" t="n">
-        <v>96390</v>
+        <v>96393</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>129909316</v>
       </c>
       <c r="B13" t="n">
-        <v>91561</v>
+        <v>91564</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 45735-2025 artfynd.xlsx
+++ b/artfynd/A 45735-2025 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>129909309</v>
       </c>
       <c r="B7" t="n">
-        <v>110742</v>
+        <v>110743</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>129909315</v>
       </c>
       <c r="B8" t="n">
-        <v>91564</v>
+        <v>91565</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>129909308</v>
       </c>
       <c r="B9" t="n">
-        <v>110742</v>
+        <v>110743</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>129909319</v>
       </c>
       <c r="B10" t="n">
-        <v>91564</v>
+        <v>91565</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>129909310</v>
       </c>
       <c r="B11" t="n">
-        <v>110742</v>
+        <v>110743</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>129909317</v>
       </c>
       <c r="B12" t="n">
-        <v>96393</v>
+        <v>96394</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>129909316</v>
       </c>
       <c r="B13" t="n">
-        <v>91564</v>
+        <v>91565</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 45735-2025 artfynd.xlsx
+++ b/artfynd/A 45735-2025 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>129909309</v>
       </c>
       <c r="B7" t="n">
-        <v>110743</v>
+        <v>110760</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>129909315</v>
       </c>
       <c r="B8" t="n">
-        <v>91565</v>
+        <v>91582</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>129909308</v>
       </c>
       <c r="B9" t="n">
-        <v>110743</v>
+        <v>110760</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>129909319</v>
       </c>
       <c r="B10" t="n">
-        <v>91565</v>
+        <v>91582</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>129909310</v>
       </c>
       <c r="B11" t="n">
-        <v>110743</v>
+        <v>110760</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>129909317</v>
       </c>
       <c r="B12" t="n">
-        <v>96394</v>
+        <v>96411</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>129909316</v>
       </c>
       <c r="B13" t="n">
-        <v>91565</v>
+        <v>91582</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 45735-2025 artfynd.xlsx
+++ b/artfynd/A 45735-2025 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>129909309</v>
       </c>
       <c r="B7" t="n">
-        <v>110776</v>
+        <v>110779</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>129909315</v>
       </c>
       <c r="B8" t="n">
-        <v>91598</v>
+        <v>91600</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>129909308</v>
       </c>
       <c r="B9" t="n">
-        <v>110776</v>
+        <v>110779</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>129909319</v>
       </c>
       <c r="B10" t="n">
-        <v>91598</v>
+        <v>91600</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>129909310</v>
       </c>
       <c r="B11" t="n">
-        <v>110776</v>
+        <v>110779</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>129909317</v>
       </c>
       <c r="B12" t="n">
-        <v>96427</v>
+        <v>96429</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>129909316</v>
       </c>
       <c r="B13" t="n">
-        <v>91598</v>
+        <v>91600</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 45735-2025 artfynd.xlsx
+++ b/artfynd/A 45735-2025 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>129909309</v>
       </c>
       <c r="B7" t="n">
-        <v>110779</v>
+        <v>110866</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>129909315</v>
       </c>
       <c r="B8" t="n">
-        <v>91600</v>
+        <v>91687</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>129909308</v>
       </c>
       <c r="B9" t="n">
-        <v>110779</v>
+        <v>110866</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>129909319</v>
       </c>
       <c r="B10" t="n">
-        <v>91600</v>
+        <v>91687</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>129909310</v>
       </c>
       <c r="B11" t="n">
-        <v>110779</v>
+        <v>110866</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>129909317</v>
       </c>
       <c r="B12" t="n">
-        <v>96429</v>
+        <v>96516</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>129909316</v>
       </c>
       <c r="B13" t="n">
-        <v>91600</v>
+        <v>91687</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 45735-2025 artfynd.xlsx
+++ b/artfynd/A 45735-2025 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>129909309</v>
       </c>
       <c r="B7" t="n">
-        <v>110866</v>
+        <v>110779</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>129909315</v>
       </c>
       <c r="B8" t="n">
-        <v>91687</v>
+        <v>91600</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>129909308</v>
       </c>
       <c r="B9" t="n">
-        <v>110866</v>
+        <v>110779</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>129909319</v>
       </c>
       <c r="B10" t="n">
-        <v>91687</v>
+        <v>91600</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>129909310</v>
       </c>
       <c r="B11" t="n">
-        <v>110866</v>
+        <v>110779</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>129909317</v>
       </c>
       <c r="B12" t="n">
-        <v>96516</v>
+        <v>96429</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>129909316</v>
       </c>
       <c r="B13" t="n">
-        <v>91687</v>
+        <v>91600</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 45735-2025 artfynd.xlsx
+++ b/artfynd/A 45735-2025 artfynd.xlsx
@@ -675,62 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>365203</v>
+        <v>129120179</v>
       </c>
       <c r="B2" t="n">
-        <v>90522</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91897</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1428</v>
+        <v>881</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rutkremla</t>
+          <t>Skillerticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Russula virescens</t>
+          <t>Inonotus cuticularis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Fr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Bull.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Knösö mellersta, Bl</t>
+          <t>Knösö N, Bl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541443.1165672482</v>
+        <v>541436</v>
       </c>
       <c r="R2" t="n">
-        <v>6225273.529635259</v>
+        <v>6225152</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2004-07-11</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2004-07-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,74 +757,76 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Trädbärande mark</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Urban Emanuelsson</t>
+          <t>Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Urban Emanuelsson</t>
+          <t>Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129120200</v>
+        <v>365203</v>
       </c>
       <c r="B3" t="n">
-        <v>85223</v>
+        <v>93082</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1971</v>
+        <v>1428</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor sotdyna</t>
+          <t>Rutkremla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Camarops polysperma</t>
+          <t>Russula virescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Mont.) J.H.Mill.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Schaeff.) Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Knösö N, Bl</t>
+          <t>Knösö mellersta, Bl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541610</v>
+        <v>541443</v>
       </c>
       <c r="R3" t="n">
-        <v>6225190</v>
+        <v>6225274</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,17 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2004-07-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På grov låga av klibbal.</t>
+          <t>2004-07-11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,29 +864,33 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Trädbärande mark</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Joakim Andersson Hemberg</t>
+          <t>Urban Emanuelsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Joakim Andersson Hemberg</t>
+          <t>Urban Emanuelsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129120162</v>
+        <v>129120200</v>
       </c>
       <c r="B4" t="n">
-        <v>92373</v>
+        <v>85532</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2014</v>
+        <v>1971</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Stor sotdyna</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Camarops polysperma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Mont.) J.H.Mill.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -945,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541667</v>
+        <v>541610</v>
       </c>
       <c r="R4" t="n">
-        <v>6225240</v>
+        <v>6225190</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -985,7 +965,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På grov boklåga.</t>
+          <t>På grov låga av klibbal.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,32 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129120179</v>
+        <v>129120162</v>
       </c>
       <c r="B5" t="n">
-        <v>91541</v>
+        <v>92732</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>881</v>
+        <v>2014</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skillerticka</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Inonotus cuticularis</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bull.) P.Karst.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541436</v>
+        <v>541667</v>
       </c>
       <c r="R5" t="n">
-        <v>6225152</v>
+        <v>6225240</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1087,6 +1067,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På grov boklåga.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129120312</v>
+        <v>129909317</v>
       </c>
       <c r="B6" t="n">
-        <v>92136</v>
+        <v>96708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1125,37 +1110,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3884</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Knösö N, Bl</t>
+          <t>Knösö, Bl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541326</v>
+        <v>541548</v>
       </c>
       <c r="R6" t="n">
-        <v>6225283</v>
+        <v>6225086</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1182,12 +1164,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1196,29 +1178,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joakim Andersson Hemberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joakim Andersson Hemberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129909309</v>
+        <v>129120312</v>
       </c>
       <c r="B7" t="n">
-        <v>110866</v>
+        <v>92497</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,34 +1207,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219677</v>
+        <v>3884</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Knösö, Bl</t>
+          <t>Knösö N, Bl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541705</v>
+        <v>541326</v>
       </c>
       <c r="R7" t="n">
-        <v>6225086</v>
+        <v>6225283</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1280,12 +1264,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1294,18 +1278,19 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1315,7 +1300,7 @@
         <v>129909315</v>
       </c>
       <c r="B8" t="n">
-        <v>91687</v>
+        <v>91867</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1409,32 +1394,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129909308</v>
+        <v>129909316</v>
       </c>
       <c r="B9" t="n">
-        <v>110866</v>
+        <v>91867</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219677</v>
+        <v>5445</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541609</v>
+        <v>541530</v>
       </c>
       <c r="R9" t="n">
-        <v>6225184</v>
+        <v>6225095</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1509,7 +1494,7 @@
         <v>129909319</v>
       </c>
       <c r="B10" t="n">
-        <v>91687</v>
+        <v>91867</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1603,10 +1588,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129909310</v>
+        <v>129909308</v>
       </c>
       <c r="B11" t="n">
-        <v>110866</v>
+        <v>111175</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1638,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>541322</v>
+        <v>541609</v>
       </c>
       <c r="R11" t="n">
-        <v>6225055</v>
+        <v>6225184</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1700,10 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129909317</v>
+        <v>129909309</v>
       </c>
       <c r="B12" t="n">
-        <v>96516</v>
+        <v>111175</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,21 +1696,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2180</v>
+        <v>219677</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,7 +1720,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541548</v>
+        <v>541705</v>
       </c>
       <c r="R12" t="n">
         <v>6225086</v>
@@ -1797,32 +1782,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129909316</v>
+        <v>129909310</v>
       </c>
       <c r="B13" t="n">
-        <v>91687</v>
+        <v>111175</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5445</v>
+        <v>219677</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1832,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541530</v>
+        <v>541322</v>
       </c>
       <c r="R13" t="n">
-        <v>6225095</v>
+        <v>6225055</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>

--- a/artfynd/A 45735-2025 artfynd.xlsx
+++ b/artfynd/A 45735-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129120179</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/365203</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129120200</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129120162</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1193,6 +1218,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129909317</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1294,6 +1324,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129120312</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1391,6 +1426,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129909315</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129909316</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1585,6 +1630,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129909319</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129909308</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1779,6 +1834,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129909309</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1876,8 +1936,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129909310</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>